--- a/artfynd/A 5084-2020 artfynd.xlsx
+++ b/artfynd/A 5084-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126289568</v>
       </c>
       <c r="B2" t="n">
-        <v>98367</v>
+        <v>98371</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>126289498</v>
       </c>
       <c r="B4" t="n">
-        <v>98262</v>
+        <v>98266</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1115,7 +1115,7 @@
         <v>126289485</v>
       </c>
       <c r="B6" t="n">
-        <v>92556</v>
+        <v>92560</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1224,7 +1224,7 @@
         <v>126289598</v>
       </c>
       <c r="B7" t="n">
-        <v>91238</v>
+        <v>91242</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 5084-2020 artfynd.xlsx
+++ b/artfynd/A 5084-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126289568</v>
       </c>
       <c r="B2" t="n">
-        <v>98371</v>
+        <v>98374</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>126289498</v>
       </c>
       <c r="B4" t="n">
-        <v>98266</v>
+        <v>98269</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 5084-2020 artfynd.xlsx
+++ b/artfynd/A 5084-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126289568</v>
       </c>
       <c r="B2" t="n">
-        <v>98374</v>
+        <v>98383</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>126289498</v>
       </c>
       <c r="B4" t="n">
-        <v>98269</v>
+        <v>98278</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1115,7 +1115,7 @@
         <v>126289485</v>
       </c>
       <c r="B6" t="n">
-        <v>92560</v>
+        <v>92563</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1224,7 +1224,7 @@
         <v>126289598</v>
       </c>
       <c r="B7" t="n">
-        <v>91242</v>
+        <v>91245</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
